--- a/data/trans_orig/Q25_A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q25_A_R-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años desde que dejó de fumar</t>
+          <t>Tiempo medio en años desde que dejó de fumar (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,83; 12,79</t>
+          <t>7,65; 12,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,9</t>
+          <t>8,45; 13,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,37; 13,8</t>
+          <t>9,32; 13,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,41; 19,27</t>
+          <t>13,45; 19,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,13</t>
+          <t>2,88; 7,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 11,6</t>
+          <t>5,49; 11,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,02; 15,29</t>
+          <t>5,91; 14,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,27; 16,25</t>
+          <t>9,57; 16,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 10,11</t>
+          <t>6,57; 10,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,39; 12,52</t>
+          <t>8,22; 12,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,59; 12,59</t>
+          <t>8,63; 12,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,96; 18,22</t>
+          <t>13,24; 17,95</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 13,17</t>
+          <t>9,46; 13,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,8; 15,64</t>
+          <t>10,79; 15,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,04; 13,51</t>
+          <t>9,05; 13,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,81; 16,67</t>
+          <t>11,85; 16,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,46</t>
+          <t>3,64; 8,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,99</t>
+          <t>5,4; 9,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 15,22</t>
+          <t>7,25; 14,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,54; 14,27</t>
+          <t>9,52; 14,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,62; 12,01</t>
+          <t>8,64; 11,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,3; 12,94</t>
+          <t>9,36; 12,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,01; 12,93</t>
+          <t>9,08; 13,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 15,01</t>
+          <t>11,46; 14,8</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,55; 14,01</t>
+          <t>9,8; 14,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,61; 13,86</t>
+          <t>9,45; 13,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,93; 16,02</t>
+          <t>11,07; 15,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,59; 18,13</t>
+          <t>12,44; 18,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,44</t>
+          <t>2,83; 6,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 8,64</t>
+          <t>4,76; 8,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,82</t>
+          <t>5,15; 9,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,87; 17,57</t>
+          <t>8,58; 17,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,64; 12,46</t>
+          <t>8,52; 12,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,55; 12,06</t>
+          <t>8,56; 12,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,46; 13,19</t>
+          <t>9,59; 13,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,55; 16,16</t>
+          <t>11,72; 16,56</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,25; 11,63</t>
+          <t>8,39; 11,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,35; 14,97</t>
+          <t>10,44; 15,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,59; 16,14</t>
+          <t>11,66; 16,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,3; 20,4</t>
+          <t>15,21; 20,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,37</t>
+          <t>4,71; 8,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 12,9</t>
+          <t>7,05; 13,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,97; 12,5</t>
+          <t>7,09; 12,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,77; 18,3</t>
+          <t>12,75; 18,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 10,02</t>
+          <t>7,47; 9,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 13,69</t>
+          <t>9,9; 13,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,63; 13,99</t>
+          <t>10,56; 14,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,2; 19,09</t>
+          <t>15,0; 18,82</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,62; 14,66</t>
+          <t>8,74; 14,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,71; 17,63</t>
+          <t>9,8; 17,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,76; 18,21</t>
+          <t>10,5; 17,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,91; 17,35</t>
+          <t>9,77; 17,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,07</t>
+          <t>3,84; 9,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 11,73</t>
+          <t>5,52; 11,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,1</t>
+          <t>2,34; 4,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 15,24</t>
+          <t>6,81; 15,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 11,28</t>
+          <t>7,29; 11,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 14,17</t>
+          <t>9,04; 14,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,48; 13,75</t>
+          <t>8,43; 13,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,71; 15,28</t>
+          <t>9,67; 15,19</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,77; 11,21</t>
+          <t>6,63; 11,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,35</t>
+          <t>9,14; 13,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,88; 15,04</t>
+          <t>9,92; 15,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,5; 19,51</t>
+          <t>13,66; 19,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,64</t>
+          <t>2,78; 5,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,0</t>
+          <t>4,06; 9,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,42; 10,43</t>
+          <t>4,4; 10,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,94; 16,51</t>
+          <t>7,23; 17,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,88; 9,22</t>
+          <t>5,98; 9,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,46; 12,51</t>
+          <t>8,52; 12,14</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,04; 13,13</t>
+          <t>8,98; 13,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,95; 17,99</t>
+          <t>12,97; 17,89</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,51; 13,24</t>
+          <t>9,62; 13,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,17; 15,07</t>
+          <t>10,98; 15,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,02; 12,47</t>
+          <t>9,13; 12,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,33; 19,65</t>
+          <t>15,39; 19,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,52; 11,83</t>
+          <t>6,52; 11,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,34</t>
+          <t>6,32; 9,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,77; 9,95</t>
+          <t>6,77; 10,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,58; 15,78</t>
+          <t>11,59; 15,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,28; 12,39</t>
+          <t>9,21; 12,37</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,74; 12,68</t>
+          <t>9,8; 12,59</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,6; 10,98</t>
+          <t>8,5; 11,02</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,26; 17,15</t>
+          <t>14,35; 17,39</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,97; 13,63</t>
+          <t>9,9; 13,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,57; 13,46</t>
+          <t>9,39; 13,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,97; 17,11</t>
+          <t>13,0; 16,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,15; 17,61</t>
+          <t>2,97; 17,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,07; 10,88</t>
+          <t>7,1; 11,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,18</t>
+          <t>5,8; 9,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,55</t>
+          <t>9,2; 13,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,48; 14,98</t>
+          <t>9,72; 15,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,31; 12,05</t>
+          <t>9,16; 12,12</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,77; 11,78</t>
+          <t>8,63; 11,45</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,05; 15,05</t>
+          <t>11,99; 15,08</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 16,16</t>
+          <t>3,33; 16,25</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,08; 11,55</t>
+          <t>10,16; 11,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1846,52 +1846,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,84; 13,43</t>
+          <t>11,78; 13,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,88; 16,69</t>
+          <t>6,12; 16,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,94; 7,71</t>
+          <t>5,96; 7,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,87; 8,49</t>
+          <t>6,97; 8,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,99; 9,96</t>
+          <t>8,0; 10,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,76; 14,09</t>
+          <t>11,83; 14,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,07; 10,24</t>
+          <t>9,11; 10,31</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10,08; 11,29</t>
+          <t>10,06; 11,27</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,7; 12,03</t>
+          <t>10,7; 11,98</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,35; 15,41</t>
+          <t>7,55; 15,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q25_A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q25_A_R-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,5</t>
+          <t>15,5</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,62</t>
+          <t>12,61</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,7</t>
+          <t>14,91</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,65; 12,51</t>
+          <t>7,69; 12,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,45; 13,67</t>
+          <t>8,71; 13,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,32; 13,87</t>
+          <t>9,11; 13,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,45; 19,35</t>
+          <t>12,83; 18,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,46</t>
+          <t>2,86; 7,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 11,94</t>
+          <t>5,7; 12,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,91; 14,41</t>
+          <t>5,97; 15,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,57; 16,31</t>
+          <t>8,98; 15,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 10,55</t>
+          <t>6,49; 10,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,22; 12,62</t>
+          <t>8,43; 12,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,63; 12,92</t>
+          <t>8,59; 12,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,24; 17,95</t>
+          <t>12,4; 17,29</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,13</t>
+          <t>14,1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,74</t>
+          <t>11,6</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,24</t>
+          <t>13,2</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,46; 13,21</t>
+          <t>9,3; 13,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,79; 15,62</t>
+          <t>10,66; 15,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 13,42</t>
+          <t>8,97; 13,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 16,44</t>
+          <t>11,93; 16,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 8,22</t>
+          <t>3,57; 8,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,16</t>
+          <t>5,38; 9,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 14,95</t>
+          <t>7,25; 14,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 14,21</t>
+          <t>9,45; 14,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 11,79</t>
+          <t>8,59; 11,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,36; 12,82</t>
+          <t>9,28; 12,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,08; 13,15</t>
+          <t>9,18; 13,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,46; 14,8</t>
+          <t>11,52; 15,04</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,23</t>
+          <t>15,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,54</t>
+          <t>10,0</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,66</t>
+          <t>12,94</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,8; 14,29</t>
+          <t>9,76; 14,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,45; 13,93</t>
+          <t>9,56; 14,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,07; 15,93</t>
+          <t>10,76; 15,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,44; 18,03</t>
+          <t>12,65; 18,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,36</t>
+          <t>2,84; 6,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,54</t>
+          <t>4,72; 8,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 9,62</t>
+          <t>5,08; 9,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,58; 17,46</t>
+          <t>8,13; 12,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,52; 12,46</t>
+          <t>8,66; 12,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,15</t>
+          <t>8,46; 11,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 13,24</t>
+          <t>9,62; 13,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,72; 16,56</t>
+          <t>11,22; 14,93</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,01</t>
+          <t>18,02</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,3</t>
+          <t>14,77</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,96</t>
+          <t>16,78</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 11,65</t>
+          <t>8,25; 11,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,44; 15,25</t>
+          <t>10,46; 15,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,66; 16,46</t>
+          <t>11,79; 16,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,21; 20,46</t>
+          <t>15,63; 20,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,4</t>
+          <t>4,89; 8,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 13,37</t>
+          <t>6,79; 12,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 12,91</t>
+          <t>7,08; 12,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,75; 18,03</t>
+          <t>12,31; 17,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 9,99</t>
+          <t>7,5; 10,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,9; 13,82</t>
+          <t>9,86; 13,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 14,17</t>
+          <t>10,5; 14,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,0; 18,82</t>
+          <t>14,95; 18,54</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,34</t>
+          <t>13,27</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,48</t>
+          <t>10,4</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,31</t>
+          <t>12,24</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,74; 14,81</t>
+          <t>8,67; 15,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,8; 17,51</t>
+          <t>9,59; 17,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,5; 17,86</t>
+          <t>10,46; 17,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,77; 17,23</t>
+          <t>9,77; 17,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 9,41</t>
+          <t>3,89; 9,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 11,87</t>
+          <t>5,7; 12,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,78</t>
+          <t>2,14; 4,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 15,42</t>
+          <t>6,71; 14,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 11,38</t>
+          <t>7,26; 11,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,04; 14,51</t>
+          <t>8,95; 14,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,43; 13,86</t>
+          <t>8,15; 13,74</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,67; 15,19</t>
+          <t>9,57; 15,23</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,39</t>
+          <t>16,68</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,4</t>
+          <t>11,46</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,42</t>
+          <t>15,61</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,63; 11,19</t>
+          <t>6,69; 11,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,14; 13,57</t>
+          <t>8,92; 13,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,92; 15,1</t>
+          <t>9,75; 15,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,66; 19,31</t>
+          <t>13,89; 19,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,68</t>
+          <t>2,76; 5,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,06; 9,65</t>
+          <t>4,25; 9,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,4; 10,25</t>
+          <t>4,41; 10,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,23; 17,06</t>
+          <t>7,25; 17,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,98; 9,43</t>
+          <t>5,87; 9,3</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,52; 12,14</t>
+          <t>8,2; 12,22</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,98; 13,42</t>
+          <t>9,03; 13,21</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,97; 17,89</t>
+          <t>13,19; 18,07</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,31</t>
+          <t>17,15</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,52</t>
+          <t>14,03</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,68</t>
+          <t>15,83</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,62; 13,29</t>
+          <t>9,63; 13,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,98; 15,05</t>
+          <t>10,99; 14,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,13; 12,47</t>
+          <t>9,13; 12,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,39; 19,5</t>
+          <t>15,1; 19,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,52; 11,57</t>
+          <t>6,47; 11,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 9,13</t>
+          <t>6,43; 9,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,77; 10,08</t>
+          <t>6,8; 10,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,59; 15,6</t>
+          <t>11,95; 16,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,21; 12,37</t>
+          <t>9,17; 12,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,8; 12,59</t>
+          <t>9,71; 12,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,5; 11,02</t>
+          <t>8,5; 10,92</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,35; 17,39</t>
+          <t>14,34; 17,41</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,42</t>
+          <t>16,9</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12,16</t>
+          <t>12,05</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,97</t>
+          <t>15,57</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,9; 13,38</t>
+          <t>9,78; 13,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,39; 13,27</t>
+          <t>9,56; 13,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,0; 16,74</t>
+          <t>12,92; 16,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,97; 17,59</t>
+          <t>15,23; 18,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,1; 11,08</t>
+          <t>7,11; 10,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,29</t>
+          <t>5,83; 9,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,2; 13,62</t>
+          <t>9,33; 13,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,72; 15,03</t>
+          <t>9,37; 14,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,16; 12,12</t>
+          <t>9,31; 12,13</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,63; 11,45</t>
+          <t>8,62; 11,5</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11,99; 15,08</t>
+          <t>12,07; 15,14</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,33; 16,25</t>
+          <t>14,01; 17,07</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12,17</t>
+          <t>16,25</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>12,71</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,37</t>
+          <t>14,99</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,16; 11,62</t>
+          <t>10,16; 11,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,28; 12,97</t>
+          <t>11,25; 12,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,78; 13,46</t>
+          <t>11,88; 13,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,12; 16,65</t>
+          <t>15,37; 17,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,96; 7,65</t>
+          <t>5,98; 7,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,97; 8,6</t>
+          <t>6,84; 8,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,0; 10,1</t>
+          <t>7,96; 9,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,83; 14,03</t>
+          <t>11,68; 13,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,11; 10,31</t>
+          <t>9,11; 10,29</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10,06; 11,27</t>
+          <t>10,03; 11,31</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10,7; 11,98</t>
+          <t>10,7; 12,01</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,55; 15,33</t>
+          <t>14,35; 15,77</t>
         </is>
       </c>
     </row>
